--- a/data/sars/atlantic/tables/Atlantic_2023_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2023_Table1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001C9254-F5E4-DF45-AE81-1EFEE8BDBE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88F0DD-D9F1-6540-A476-D74B53F1C35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5060" yWindow="500" windowWidth="27400" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="151">
   <si>
     <t>North Atlantic right whale</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>True’s beaked whale</t>
-  </si>
-  <si>
-    <t>3, 391</t>
   </si>
   <si>
     <t>Melon-headed whale</t>
@@ -708,70 +705,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1085,7 +1082,9 @@
     <col min="2" max="2" width="28.3984375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="79" style="5" customWidth="1"/>
     <col min="4" max="4" width="14.59765625" style="5" customWidth="1"/>
-    <col min="5" max="9" width="11.19921875" style="5" customWidth="1"/>
+    <col min="5" max="6" width="11.19921875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.796875" style="5" customWidth="1"/>
+    <col min="8" max="9" width="11.19921875" style="5" customWidth="1"/>
     <col min="10" max="10" width="9.19921875" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.796875" style="5" customWidth="1"/>
     <col min="12" max="13" width="18" style="5" customWidth="1"/>
@@ -1100,58 +1099,58 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q1" s="19" t="s">
+      <c r="R1" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="S1" s="4"/>
     </row>
@@ -1163,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>1</v>
@@ -1213,10 +1212,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>3</v>
@@ -1269,7 +1268,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1</v>
@@ -1375,7 +1374,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>1</v>
@@ -1428,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>3</v>
@@ -1465,7 +1464,7 @@
         <v>2019</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q7" s="20"/>
       <c r="R7" s="8" t="s">
@@ -1481,7 +1480,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>1</v>
@@ -1534,7 +1533,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>1</v>
@@ -1589,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1</v>
@@ -1644,7 +1643,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>3</v>
@@ -1697,7 +1696,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>1</v>
@@ -1750,7 +1749,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1</v>
@@ -1800,10 +1799,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>3</v>
@@ -1854,7 +1853,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>1</v>
@@ -1905,7 +1904,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1</v>
@@ -1916,8 +1915,8 @@
       <c r="F16" s="9">
         <v>0.26</v>
       </c>
-      <c r="G16" s="18">
-        <v>2.3740000000000001</v>
+      <c r="G16" s="22">
+        <v>2374</v>
       </c>
       <c r="H16" s="9">
         <v>0.04</v>
@@ -1956,7 +1955,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>1</v>
@@ -2007,7 +2006,7 @@
         <v>21</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>1</v>
@@ -2058,7 +2057,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>1</v>
@@ -2069,8 +2068,8 @@
       <c r="F19" s="9">
         <v>0.34</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>23</v>
+      <c r="G19" s="22">
+        <v>3391</v>
       </c>
       <c r="H19" s="9">
         <v>0.04</v>
@@ -2106,10 +2105,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>1</v>
@@ -2157,10 +2156,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>1</v>
@@ -2210,10 +2209,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1</v>
@@ -2263,10 +2262,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>1</v>
@@ -2316,10 +2315,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1</v>
@@ -2369,10 +2368,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>3</v>
@@ -2420,10 +2419,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>1</v>
@@ -2473,10 +2472,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1</v>
@@ -2524,10 +2523,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>1</v>
@@ -2575,10 +2574,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>1</v>
@@ -2626,10 +2625,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>1</v>
@@ -2677,10 +2676,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1</v>
@@ -2701,7 +2700,7 @@
         <v>0.5</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K31" s="6">
         <v>0</v>
@@ -2728,10 +2727,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1</v>
@@ -2779,10 +2778,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>1</v>
@@ -2830,10 +2829,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>1</v>
@@ -2875,7 +2874,7 @@
         <v>2021</v>
       </c>
       <c r="Q34" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R34" s="7" t="s">
         <v>13</v>
@@ -2886,10 +2885,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>3</v>
@@ -2913,10 +2912,10 @@
         <v>48</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M35" s="8"/>
       <c r="N35" s="8" t="s">
@@ -2937,10 +2936,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>3</v>
@@ -2964,10 +2963,10 @@
         <v>24</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8" t="s">
@@ -2988,10 +2987,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>3</v>
@@ -3015,10 +3014,10 @@
         <v>46</v>
       </c>
       <c r="K37" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>43</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="M37" s="8"/>
       <c r="N37" s="8" t="s">
@@ -3039,10 +3038,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>3</v>
@@ -3090,10 +3089,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>3</v>
@@ -3141,10 +3140,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>3</v>
@@ -3168,10 +3167,10 @@
         <v>7.8</v>
       </c>
       <c r="K40" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="M40" s="8"/>
       <c r="N40" s="8" t="s">
@@ -3192,10 +3191,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>3</v>
@@ -3216,7 +3215,7 @@
         <v>0.5</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K41" s="10">
         <v>0.4</v>
@@ -3243,10 +3242,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>3</v>
@@ -3294,10 +3293,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>3</v>
@@ -3318,7 +3317,7 @@
         <v>0.5</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K43" s="10">
         <v>2.2000000000000002</v>
@@ -3334,7 +3333,7 @@
         <v>2022</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R43" s="8" t="s">
         <v>13</v>
@@ -3345,10 +3344,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>3</v>
@@ -3385,7 +3384,7 @@
         <v>2022</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R44" s="8" t="s">
         <v>13</v>
@@ -3396,10 +3395,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>3</v>
@@ -3420,7 +3419,7 @@
         <v>0.5</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K45" s="15">
         <v>0.4</v>
@@ -3436,7 +3435,7 @@
         <v>2022</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R45" s="7" t="s">
         <v>13</v>
@@ -3447,10 +3446,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>3</v>
@@ -3471,7 +3470,7 @@
         <v>0.5</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K46" s="15">
         <v>0.1</v>
@@ -3487,7 +3486,7 @@
         <v>2022</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R46" s="7" t="s">
         <v>13</v>
@@ -3498,10 +3497,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>3</v>
@@ -3538,7 +3537,7 @@
         <v>2022</v>
       </c>
       <c r="P47" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R47" s="8" t="s">
         <v>13</v>
@@ -3549,10 +3548,10 @@
         <v>68</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>3</v>
@@ -3589,7 +3588,7 @@
         <v>2021</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R48" s="8" t="s">
         <v>13</v>
@@ -3600,10 +3599,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>3</v>
@@ -3640,7 +3639,7 @@
         <v>2022</v>
       </c>
       <c r="P49" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R49" s="8" t="s">
         <v>13</v>
@@ -3651,10 +3650,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>1</v>
@@ -3704,10 +3703,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>3</v>
@@ -3757,10 +3756,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>1</v>
@@ -3810,10 +3809,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>3</v>
@@ -3863,10 +3862,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>3</v>
@@ -3905,7 +3904,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R54" s="8" t="s">
         <v>2</v>
@@ -3916,10 +3915,10 @@
         <v>47</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>3</v>
@@ -3956,7 +3955,7 @@
         <v>2022</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R55" s="7" t="s">
         <v>13</v>
@@ -3967,10 +3966,10 @@
         <v>75</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>3</v>
@@ -4007,10 +4006,10 @@
         <v>2021</v>
       </c>
       <c r="P56" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>13</v>
@@ -4024,7 +4023,7 @@
         <v>10</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>3</v>
@@ -4063,7 +4062,7 @@
         <v>2020</v>
       </c>
       <c r="P57" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q57" s="20"/>
       <c r="R57" s="7" t="s">
@@ -4075,10 +4074,10 @@
         <v>55</v>
       </c>
       <c r="B58" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>3</v>
@@ -4115,10 +4114,10 @@
         <v>2022</v>
       </c>
       <c r="P58" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q58" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R58" s="8" t="s">
         <v>13</v>
@@ -4132,7 +4131,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>3</v>
@@ -4169,7 +4168,7 @@
         <v>2020</v>
       </c>
       <c r="P59" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q59" s="20"/>
       <c r="R59" s="7" t="s">
@@ -4184,7 +4183,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>3</v>
@@ -4221,10 +4220,10 @@
         <v>2020</v>
       </c>
       <c r="P60" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q60" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R60" s="7" t="s">
         <v>13</v>
@@ -4235,10 +4234,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>3</v>
@@ -4275,7 +4274,7 @@
         <v>2020</v>
       </c>
       <c r="P61" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q61" s="20"/>
       <c r="R61" s="7" t="s">
@@ -4287,10 +4286,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>3</v>
@@ -4327,10 +4326,10 @@
         <v>2021</v>
       </c>
       <c r="P62" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q62" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R62" s="8" t="s">
         <v>13</v>
@@ -4341,10 +4340,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>3</v>
@@ -4381,7 +4380,7 @@
         <v>2021</v>
       </c>
       <c r="P63" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R63" s="7" t="s">
         <v>13</v>
@@ -4392,10 +4391,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>3</v>
@@ -4432,7 +4431,7 @@
         <v>2021</v>
       </c>
       <c r="P64" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R64" s="7" t="s">
         <v>13</v>
@@ -4443,10 +4442,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>3</v>
@@ -4467,7 +4466,7 @@
         <v>0.4</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K65" s="10">
         <v>0.8</v>
@@ -4486,7 +4485,7 @@
         <v>1992</v>
       </c>
       <c r="Q65" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R65" s="8" t="s">
         <v>13</v>
@@ -4497,10 +4496,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>3</v>
@@ -4521,7 +4520,7 @@
         <v>0.4</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K66" s="10">
         <v>0.2</v>
@@ -4540,7 +4539,7 @@
         <v>1992</v>
       </c>
       <c r="Q66" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R66" s="8" t="s">
         <v>13</v>
@@ -4551,10 +4550,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>3</v>
@@ -4575,7 +4574,7 @@
         <v>0.4</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K67" s="10">
         <v>0.6</v>
@@ -4594,7 +4593,7 @@
         <v>1992</v>
       </c>
       <c r="Q67" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R67" s="8" t="s">
         <v>13</v>
@@ -4605,10 +4604,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>3</v>
@@ -4629,7 +4628,7 @@
         <v>0.4</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K68" s="10">
         <v>0.4</v>
@@ -4648,7 +4647,7 @@
         <v>1992</v>
       </c>
       <c r="Q68" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R68" s="8" t="s">
         <v>13</v>
@@ -4659,10 +4658,10 @@
         <v>62</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>3</v>
@@ -4699,7 +4698,7 @@
         <v>2021</v>
       </c>
       <c r="P69" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>13</v>
@@ -4710,10 +4709,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>3</v>
@@ -4761,10 +4760,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>3</v>
@@ -4804,7 +4803,7 @@
         <v>2017</v>
       </c>
       <c r="Q71" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R71" s="8" t="s">
         <v>13</v>
@@ -4815,22 +4814,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="6">
+        <v>0</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="6">
-        <v>0</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="G72" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H72" s="9">
         <v>0.04</v>
@@ -4839,7 +4838,7 @@
         <v>0.45</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K72" s="10">
         <v>0.2</v>
@@ -4858,7 +4857,7 @@
         <v>1992</v>
       </c>
       <c r="Q72" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R72" s="8" t="s">
         <v>13</v>
@@ -4869,10 +4868,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>3</v>
@@ -4881,10 +4880,10 @@
         <v>0</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H73" s="9">
         <v>0.04</v>
@@ -4893,7 +4892,7 @@
         <v>0.45</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K73" s="6">
         <v>0</v>
@@ -4912,7 +4911,7 @@
         <v>1992</v>
       </c>
       <c r="Q73" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R73" s="8" t="s">
         <v>13</v>
@@ -4923,10 +4922,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>3</v>
@@ -4974,10 +4973,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>1</v>
@@ -5025,10 +5024,10 @@
         <v>63</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>3</v>
@@ -5065,7 +5064,7 @@
         <v>2020</v>
       </c>
       <c r="P76" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R76" s="8" t="s">
         <v>13</v>
@@ -5076,10 +5075,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>3</v>
@@ -5127,10 +5126,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>3</v>
@@ -5151,7 +5150,7 @@
         <v>0.45</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K78" s="10">
         <v>16</v>
@@ -5170,7 +5169,7 @@
         <v>1993</v>
       </c>
       <c r="Q78" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R78" s="8" t="s">
         <v>13</v>
@@ -5181,10 +5180,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>3</v>
@@ -5193,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H79" s="9">
         <v>0.04</v>
@@ -5205,7 +5204,7 @@
         <v>0.4</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K79" s="10">
         <v>0.8</v>
@@ -5224,7 +5223,7 @@
         <v>1993</v>
       </c>
       <c r="Q79" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R79" s="8" t="s">
         <v>13</v>
@@ -5235,10 +5234,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>3</v>
@@ -5259,7 +5258,7 @@
         <v>0.4</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K80" s="10">
         <v>0.4</v>
@@ -5278,7 +5277,7 @@
         <v>1993</v>
       </c>
       <c r="Q80" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R80" s="8" t="s">
         <v>13</v>
@@ -5289,10 +5288,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>3</v>
@@ -5313,7 +5312,7 @@
         <v>0.5</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K81" s="10">
         <v>0.4</v>
@@ -5340,10 +5339,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>3</v>
@@ -5391,10 +5390,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>3</v>
@@ -5442,10 +5441,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>3</v>
@@ -5466,7 +5465,7 @@
         <v>0.4</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K84" s="10">
         <v>0.2</v>
@@ -5485,7 +5484,7 @@
         <v>2007</v>
       </c>
       <c r="Q84" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R84" s="8" t="s">
         <v>13</v>
@@ -5496,10 +5495,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>3</v>
@@ -5520,7 +5519,7 @@
         <v>0.4</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K85" s="6">
         <v>0</v>
@@ -5539,7 +5538,7 @@
         <v>1993</v>
       </c>
       <c r="Q85" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R85" s="8" t="s">
         <v>13</v>
@@ -5550,10 +5549,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>3</v>
@@ -5562,7 +5561,7 @@
         <v>9</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>9</v>
@@ -5574,7 +5573,7 @@
         <v>0.4</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K86" s="10">
         <v>0.4</v>
@@ -5590,10 +5589,10 @@
         <v>2021</v>
       </c>
       <c r="P86" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q86" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R86" s="8" t="s">
         <v>13</v>
@@ -5604,10 +5603,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>3</v>
@@ -5616,7 +5615,7 @@
         <v>9</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>9</v>
@@ -5628,7 +5627,7 @@
         <v>0.4</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K87" s="10">
         <v>0.8</v>
@@ -5644,10 +5643,10 @@
         <v>2021</v>
       </c>
       <c r="P87" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q87" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R87" s="8" t="s">
         <v>13</v>
@@ -5658,10 +5657,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>3</v>
@@ -5670,7 +5669,7 @@
         <v>9</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>9</v>
@@ -5682,7 +5681,7 @@
         <v>0.4</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K88" s="10">
         <v>3</v>
@@ -5698,10 +5697,10 @@
         <v>2021</v>
       </c>
       <c r="P88" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q88" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R88" s="8" t="s">
         <v>13</v>
@@ -5712,10 +5711,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>3</v>
@@ -5755,7 +5754,7 @@
         <v>2015</v>
       </c>
       <c r="Q89" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R89" s="8" t="s">
         <v>13</v>
@@ -5766,10 +5765,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>3</v>
@@ -5790,7 +5789,7 @@
         <v>0.4</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K90" s="10">
         <v>1</v>
@@ -5809,7 +5808,7 @@
         <v>2006</v>
       </c>
       <c r="Q90" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R90" s="8" t="s">
         <v>13</v>
@@ -5820,10 +5819,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>3</v>
@@ -5832,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H91" s="9">
         <v>0.04</v>
@@ -5844,7 +5843,7 @@
         <v>0.4</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K91" s="10">
         <v>0.4</v>
@@ -5863,7 +5862,7 @@
         <v>1985</v>
       </c>
       <c r="Q91" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R91" s="8" t="s">
         <v>13</v>
@@ -5874,10 +5873,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>3</v>
@@ -5886,7 +5885,7 @@
         <v>9</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>9</v>
@@ -5898,7 +5897,7 @@
         <v>0.4</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K92" s="10">
         <v>0.4</v>
@@ -5914,10 +5913,10 @@
         <v>2021</v>
       </c>
       <c r="P92" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q92" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R92" s="8" t="s">
         <v>13</v>
@@ -5928,10 +5927,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>3</v>
@@ -5940,7 +5939,7 @@
         <v>9</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>9</v>
@@ -5952,7 +5951,7 @@
         <v>0.4</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K93" s="10">
         <v>0.2</v>
@@ -5968,10 +5967,10 @@
         <v>2021</v>
       </c>
       <c r="P93" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q93" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R93" s="8" t="s">
         <v>13</v>
@@ -5982,10 +5981,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>3</v>
@@ -5994,7 +5993,7 @@
         <v>9</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>9</v>
@@ -6006,7 +6005,7 @@
         <v>0.4</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K94" s="6">
         <v>0</v>
@@ -6022,10 +6021,10 @@
         <v>2021</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q94" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R94" s="8" t="s">
         <v>13</v>
@@ -6036,10 +6035,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>3</v>
@@ -6087,10 +6086,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>3</v>
@@ -6099,7 +6098,7 @@
         <v>9</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>9</v>
@@ -6111,7 +6110,7 @@
         <v>0.4</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K96" s="10">
         <v>0.2</v>
@@ -6127,10 +6126,10 @@
         <v>2021</v>
       </c>
       <c r="P96" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q96" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R96" s="8" t="s">
         <v>13</v>
@@ -6141,10 +6140,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>3</v>
@@ -6183,10 +6182,10 @@
         <v>2021</v>
       </c>
       <c r="P97" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q97" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R97" s="8" t="s">
         <v>13</v>
@@ -6197,10 +6196,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>3</v>
@@ -6237,7 +6236,7 @@
         <v>2020</v>
       </c>
       <c r="P98" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q98" s="20"/>
       <c r="R98" s="7" t="s">
@@ -6249,10 +6248,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>3</v>
@@ -6289,7 +6288,7 @@
         <v>2020</v>
       </c>
       <c r="P99" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q99" s="20"/>
       <c r="R99" s="7" t="s">
@@ -6301,10 +6300,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>3</v>
@@ -6341,7 +6340,7 @@
         <v>2020</v>
       </c>
       <c r="P100" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q100" s="20"/>
       <c r="R100" s="7" t="s">
@@ -6353,10 +6352,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>3</v>
@@ -6365,7 +6364,7 @@
         <v>9</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>9</v>
@@ -6377,7 +6376,7 @@
         <v>0.4</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K101" s="11">
         <v>39</v>
@@ -6395,7 +6394,7 @@
         <v>2020</v>
       </c>
       <c r="P101" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q101" s="20"/>
       <c r="R101" s="7" t="s">
@@ -6407,10 +6406,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>3</v>
@@ -6447,7 +6446,7 @@
         <v>2020</v>
       </c>
       <c r="P102" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q102" s="20"/>
       <c r="R102" s="7" t="s">
@@ -6459,10 +6458,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>3</v>
@@ -6499,7 +6498,7 @@
         <v>2020</v>
       </c>
       <c r="P103" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q103" s="20"/>
       <c r="R103" s="7" t="s">
@@ -6514,7 +6513,7 @@
         <v>15</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>3</v>
@@ -6551,7 +6550,7 @@
         <v>2020</v>
       </c>
       <c r="P104" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q104" s="20"/>
       <c r="R104" s="7" t="s">
@@ -6566,7 +6565,7 @@
         <v>17</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>3</v>
@@ -6603,7 +6602,7 @@
         <v>2020</v>
       </c>
       <c r="P105" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q105" s="20"/>
       <c r="R105" s="7" t="s">
@@ -6618,7 +6617,7 @@
         <v>16</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>3</v>
@@ -6655,7 +6654,7 @@
         <v>2020</v>
       </c>
       <c r="P106" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q106" s="20"/>
       <c r="R106" s="7" t="s">
@@ -6670,7 +6669,7 @@
         <v>11</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>3</v>
@@ -6707,10 +6706,10 @@
         <v>2020</v>
       </c>
       <c r="P107" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q107" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R107" s="7" t="s">
         <v>13</v>
@@ -6724,7 +6723,7 @@
         <v>14</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>3</v>
@@ -6761,10 +6760,10 @@
         <v>2020</v>
       </c>
       <c r="P108" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q108" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R108" s="7" t="s">
         <v>13</v>
@@ -6775,10 +6774,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>3</v>
@@ -6815,7 +6814,7 @@
         <v>2020</v>
       </c>
       <c r="P109" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q109" s="20"/>
       <c r="R109" s="7" t="s">
@@ -6827,10 +6826,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>3</v>
@@ -6867,7 +6866,7 @@
         <v>2020</v>
       </c>
       <c r="P110" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q110" s="20"/>
       <c r="R110" s="7" t="s">
@@ -6879,10 +6878,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>3</v>
@@ -6921,10 +6920,10 @@
         <v>2020</v>
       </c>
       <c r="P111" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q111" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R111" s="8" t="s">
         <v>13</v>
@@ -6935,10 +6934,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>3</v>
@@ -6975,7 +6974,7 @@
         <v>2010</v>
       </c>
       <c r="P112" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R112" s="7" t="s">
         <v>13</v>
@@ -6986,10 +6985,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>3</v>
@@ -7026,7 +7025,7 @@
         <v>2011</v>
       </c>
       <c r="P113" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R113" s="7" t="s">
         <v>13</v>
@@ -7040,7 +7039,7 @@
         <v>18</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>3</v>
@@ -7077,7 +7076,7 @@
         <v>2011</v>
       </c>
       <c r="P114" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R114" s="7" t="s">
         <v>13</v>
@@ -7088,10 +7087,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>3</v>
@@ -7128,7 +7127,7 @@
         <v>2011</v>
       </c>
       <c r="P115" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R115" s="7" t="s">
         <v>13</v>
@@ -7139,10 +7138,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>3</v>
@@ -7179,7 +7178,7 @@
         <v>2011</v>
       </c>
       <c r="P116" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R116" s="7" t="s">
         <v>13</v>
@@ -7190,10 +7189,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>3</v>
@@ -7230,7 +7229,7 @@
         <v>2011</v>
       </c>
       <c r="P117" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R117" s="7" t="s">
         <v>13</v>
@@ -7238,11 +7237,7 @@
       <c r="S117" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R117" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:R111">
-      <sortCondition ref="P1:P117"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:R117" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>